--- a/excels/BOM_FILE_3D.xlsx
+++ b/excels/BOM_FILE_3D.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\radin\Documents\Adi Heavy\Siraal\excels\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB957FC-DC21-42F3-BA34-5A7181DF5AC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3B6F345-94C8-4BAF-B8FB-DFE6B3A78E9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1365,7 +1365,7 @@
         <v>30</v>
       </c>
       <c r="H5" s="2">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
@@ -1381,11 +1381,11 @@
       </c>
       <c r="M5" s="5">
         <f>ROUND(PI()*((E5*F5/2+F5)^2-(H5/2)^2)*G5*7.87/1000000000,3)</f>
-        <v>8.9999999999999993E-3</v>
+        <v>-0.17599999999999999</v>
       </c>
       <c r="N5" s="6">
         <f>ROUND(M5*125,2)</f>
-        <v>1.1299999999999999</v>
+        <v>-22</v>
       </c>
       <c r="O5" s="7" t="s">
         <v>28</v>
@@ -1922,11 +1922,11 @@
       <c r="L25" s="62"/>
       <c r="M25" s="43">
         <f>SUM(M4:M24)</f>
-        <v>15.262999999999998</v>
+        <v>15.077999999999999</v>
       </c>
       <c r="N25" s="44">
         <f>SUM(N4:N24)</f>
-        <v>4566.17</v>
+        <v>4543.04</v>
       </c>
     </row>
   </sheetData>
